--- a/output/福島県_精神医療指標抽出.xlsx
+++ b/output/福島県_精神医療指標抽出.xlsx
@@ -11,7 +11,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_平均生活日数" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_再入院率" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_長期入院患者" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_別表第四" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_630調査R5" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_別表第四" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -60,7 +61,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -80,6 +81,16 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00F7FAFC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2EFDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DDEBF7"/>
       </patternFill>
     </fill>
     <fill>
@@ -114,7 +125,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -158,7 +169,28 @@
     <xf numFmtId="165" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
   </cellXfs>
@@ -526,7 +558,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -640,41 +672,63 @@
     <row r="9" ht="34" customHeight="1">
       <c r="A9" s="5" t="inlineStr">
         <is>
+          <t>05_630調査R5</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>第二の二の2、別表第四のC</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>630調査 Ⅲ.2.(11)・Ⅲ.2.(4)・Ⅲ.4.(1)</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>令和5年6月30日現在の在院患者数。住所地ベースの1年以上入院患者数がCに相当</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="34" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
           <t>04_別表第四</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>別表第四 一〜三の項</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr">
         <is>
           <t>付表3.3から集計</t>
         </is>
       </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="D10" s="4" t="inlineStr">
         <is>
           <t>別表第四の記号への当てはめと、算定に不足している要素の一覧</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="6" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>抽出元</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>通常集計：a988ab72-Tables_f2013_2023_ver1.0.xlsx</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>通常集計：a988ab72-Tables_f2013_2023_ver1.0.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>公費含む：f5e69661-Tables_f2023_kohi_ver1.0.xlsx</t>
         </is>
@@ -685,8 +739,8 @@
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A12:D12"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
     <mergeCell ref="A13:D13"/>
+    <mergeCell ref="A14:D14"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8234,6 +8288,532 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:F34"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>精神保健福祉資料（630調査）令和5年度・福島県</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>令和5年6月30日午前0時現在。別表第四のCは「令和五年における精神病床における入院期間が1年以上である入院患者数」であり、A1〜B2が「当該都道府県の区域に住所を有する者」を前提としていることから、住所地ベースの値を採るのが整合的。単位：人（実人数）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>1. 在院患者数（入院期間×住所地・施設所在地×年齢）　Ⅲ.2.(11)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="30" customHeight="1">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>入院期間</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>住所地
+65歳未満</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>住所地
+65歳以上</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>所在地
+65歳未満</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>所在地
+65歳以上</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>住所地 計</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>3ヶ月未満</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="n">
+        <v>392</v>
+      </c>
+      <c r="C7" s="8" t="n">
+        <v>421</v>
+      </c>
+      <c r="D7" s="8" t="n">
+        <v>384</v>
+      </c>
+      <c r="E7" s="8" t="n">
+        <v>417</v>
+      </c>
+      <c r="F7" s="8" t="n">
+        <v>813</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>3ヶ月以上12ヶ月未満</t>
+        </is>
+      </c>
+      <c r="B8" s="11" t="n">
+        <v>235</v>
+      </c>
+      <c r="C8" s="11" t="n">
+        <v>504</v>
+      </c>
+      <c r="D8" s="11" t="n">
+        <v>237</v>
+      </c>
+      <c r="E8" s="11" t="n">
+        <v>497</v>
+      </c>
+      <c r="F8" s="11" t="n">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="15" t="inlineStr">
+        <is>
+          <t>1年以上</t>
+        </is>
+      </c>
+      <c r="B9" s="16" t="n">
+        <v>901</v>
+      </c>
+      <c r="C9" s="16" t="n">
+        <v>1690</v>
+      </c>
+      <c r="D9" s="16" t="n">
+        <v>891</v>
+      </c>
+      <c r="E9" s="16" t="n">
+        <v>1651</v>
+      </c>
+      <c r="F9" s="16" t="n">
+        <v>2591</v>
+      </c>
+    </row>
+    <row r="10" ht="34" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>※「1年以上」の住所地計が別表第四のCに相当する。福島県第7期障がい福祉計画が掲げる長期在院者数（令和4年度 65歳未満995人・65歳以上1,813人）と同じ系統であり、Cは630調査の住所地ベース実人数と解される。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>2. 在院患者数（年齢階級別）　Ⅲ.2.(4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="30" customHeight="1">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>年齢階級</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>男性</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>女性</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>計</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>20歳未満</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="C14" s="8" t="n">
+        <v>31</v>
+      </c>
+      <c r="D14" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="8" t="n">
+        <v>40</v>
+      </c>
+      <c r="F14" s="4" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>20歳以上40歳未満</t>
+        </is>
+      </c>
+      <c r="B15" s="11" t="n">
+        <v>125</v>
+      </c>
+      <c r="C15" s="11" t="n">
+        <v>120</v>
+      </c>
+      <c r="D15" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="11" t="n">
+        <v>245</v>
+      </c>
+      <c r="F15" s="5" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>40歳以上65歳未満</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="n">
+        <v>697</v>
+      </c>
+      <c r="C16" s="8" t="n">
+        <v>530</v>
+      </c>
+      <c r="D16" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="8" t="n">
+        <v>1227</v>
+      </c>
+      <c r="F16" s="4" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>65歳以上75歳未満</t>
+        </is>
+      </c>
+      <c r="B17" s="11" t="n">
+        <v>633</v>
+      </c>
+      <c r="C17" s="11" t="n">
+        <v>542</v>
+      </c>
+      <c r="D17" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="11" t="n">
+        <v>1175</v>
+      </c>
+      <c r="F17" s="5" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>75歳以上</t>
+        </is>
+      </c>
+      <c r="B18" s="8" t="n">
+        <v>540</v>
+      </c>
+      <c r="C18" s="8" t="n">
+        <v>850</v>
+      </c>
+      <c r="D18" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="8" t="n">
+        <v>1390</v>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>第8期で新設された目標区分。ただし在院期間との交差表がない</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="B19" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="5" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="17" t="inlineStr">
+        <is>
+          <t>総数</t>
+        </is>
+      </c>
+      <c r="B20" s="18" t="n"/>
+      <c r="C20" s="18" t="n"/>
+      <c r="D20" s="18" t="n"/>
+      <c r="E20" s="18" t="n">
+        <v>4077</v>
+      </c>
+      <c r="F20" s="17" t="inlineStr">
+        <is>
+          <t>全在院期間の合計</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>3. 認知症治療病棟の在院患者数（在院期間別）　Ⅲ.4.(1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="30" customHeight="1">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>在院期間</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>患者数</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr"/>
+      <c r="D23" s="3" t="inlineStr"/>
+      <c r="E23" s="3" t="inlineStr"/>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>合計</t>
+        </is>
+      </c>
+      <c r="B24" s="8" t="n">
+        <v>503</v>
+      </c>
+      <c r="C24" s="19" t="n"/>
+      <c r="D24" s="19" t="n"/>
+      <c r="E24" s="19" t="n"/>
+      <c r="F24" s="4" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>1ヶ月未満</t>
+        </is>
+      </c>
+      <c r="B25" s="11" t="n">
+        <v>19</v>
+      </c>
+      <c r="C25" s="20" t="n"/>
+      <c r="D25" s="20" t="n"/>
+      <c r="E25" s="20" t="n"/>
+      <c r="F25" s="5" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>1ヶ月以上3ヶ月未満</t>
+        </is>
+      </c>
+      <c r="B26" s="8" t="n">
+        <v>46</v>
+      </c>
+      <c r="C26" s="19" t="n"/>
+      <c r="D26" s="19" t="n"/>
+      <c r="E26" s="19" t="n"/>
+      <c r="F26" s="4" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>3ヶ月以上6ヶ月未満</t>
+        </is>
+      </c>
+      <c r="B27" s="11" t="n">
+        <v>50</v>
+      </c>
+      <c r="C27" s="20" t="n"/>
+      <c r="D27" s="20" t="n"/>
+      <c r="E27" s="20" t="n"/>
+      <c r="F27" s="5" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>6ヶ月以上1年未満</t>
+        </is>
+      </c>
+      <c r="B28" s="8" t="n">
+        <v>73</v>
+      </c>
+      <c r="C28" s="19" t="n"/>
+      <c r="D28" s="19" t="n"/>
+      <c r="E28" s="19" t="n"/>
+      <c r="F28" s="4" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>1年以上5年未満</t>
+        </is>
+      </c>
+      <c r="B29" s="11" t="n">
+        <v>185</v>
+      </c>
+      <c r="C29" s="20" t="n"/>
+      <c r="D29" s="20" t="n"/>
+      <c r="E29" s="20" t="n"/>
+      <c r="F29" s="5" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>5年以上10年未満</t>
+        </is>
+      </c>
+      <c r="B30" s="8" t="n">
+        <v>65</v>
+      </c>
+      <c r="C30" s="19" t="n"/>
+      <c r="D30" s="19" t="n"/>
+      <c r="E30" s="19" t="n"/>
+      <c r="F30" s="4" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>10年以上20年未満</t>
+        </is>
+      </c>
+      <c r="B31" s="11" t="n">
+        <v>36</v>
+      </c>
+      <c r="C31" s="20" t="n"/>
+      <c r="D31" s="20" t="n"/>
+      <c r="E31" s="20" t="n"/>
+      <c r="F31" s="5" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>20年以上</t>
+        </is>
+      </c>
+      <c r="B32" s="8" t="n">
+        <v>29</v>
+      </c>
+      <c r="C32" s="19" t="n"/>
+      <c r="D32" s="19" t="n"/>
+      <c r="E32" s="19" t="n"/>
+      <c r="F32" s="4" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="B33" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C33" s="20" t="n"/>
+      <c r="D33" s="20" t="n"/>
+      <c r="E33" s="20" t="n"/>
+      <c r="F33" s="5" t="inlineStr"/>
+    </row>
+    <row r="34" ht="34" customHeight="1">
+      <c r="A34" s="17" t="inlineStr">
+        <is>
+          <t>うち1年以上</t>
+        </is>
+      </c>
+      <c r="B34" s="18" t="n">
+        <v>315</v>
+      </c>
+      <c r="C34" s="21" t="n"/>
+      <c r="D34" s="21" t="n"/>
+      <c r="E34" s="21" t="n"/>
+      <c r="F34" s="17" t="inlineStr">
+        <is>
+          <t>認知症治療病棟に限った数であり、別表第四の「認知症である者」とは一致しない（一般精神病棟にも認知症患者がいる）。認知症区分での按分にはNDB付表3.3を用いる</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A10:F10"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A22:F22"/>
+    <mergeCell ref="A12:F12"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:E31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -8603,7 +9183,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="15" t="inlineStr">
+      <c r="A23" s="22" t="inlineStr">
         <is>
           <t>算定に不足している要素</t>
         </is>
@@ -8757,17 +9337,17 @@
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>福島県第7期計画の長期在院者数は630調査ベースであり、本ブックのNDB値と定義が異なる</t>
+          <t>福島県第7期計画の長期在院者数は630調査ベースであり、NDBの1日平均在院患者数と定義が異なる</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>国が示す算定要領、または福島県への照会</t>
+          <t>令和5年度630調査 Ⅲ.2.(11) の住所地ベース1年以上入院患者数（65歳未満901人・65歳以上1,690人・計2,591人）が県計画と同系統。Cはこれと解する</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>解消</t>
         </is>
       </c>
     </row>
@@ -8784,17 +9364,17 @@
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>別表第四のCは「令和五年における」入院患者数。受領済みの630調査は令和7年度</t>
+          <t>別表第四のCは「令和五年における」入院患者数</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>国立精神・神経医療研究センター 精神保健福祉資料</t>
+          <t>受領済み（05_630調査R5シート）</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>未入手</t>
+          <t>解消</t>
         </is>
       </c>
     </row>

--- a/output/福島県_精神医療指標抽出.xlsx
+++ b/output/福島県_精神医療指標抽出.xlsx
@@ -12,7 +12,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_再入院率" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_長期入院患者" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_630調査R5" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_別表第四" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_村の在院者" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_別表第四" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -558,7 +559,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -694,41 +695,63 @@
     <row r="10" ht="34" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
+          <t>06_村の在院者</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>別表第二 三の項㈠⑤</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>ReMHRAD 市町村タブ</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>患者住所地が北塩原村である在院者数と入院先。村の基盤整備量を実数で定める起点</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="34" customHeight="1">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
           <t>04_別表第四</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B11" s="5" t="inlineStr">
         <is>
           <t>別表第四 一〜三の項</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="C11" s="5" t="inlineStr">
         <is>
           <t>付表3.3から集計</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="D11" s="5" t="inlineStr">
         <is>
           <t>別表第四の記号への当てはめと、算定に不足している要素の一覧</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="6" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>抽出元</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>通常集計：a988ab72-Tables_f2013_2023_ver1.0.xlsx</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>通常集計：a988ab72-Tables_f2013_2023_ver1.0.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>公費含む：f5e69661-Tables_f2023_kohi_ver1.0.xlsx</t>
         </is>
@@ -737,7 +760,7 @@
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A12:D12"/>
+    <mergeCell ref="A15:D15"/>
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="A13:D13"/>
     <mergeCell ref="A14:D14"/>
@@ -8814,6 +8837,159 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:E12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>北塩原村の住民のうち精神病床に入院している方（ReMHRAD）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>ReMHRAD 市町村タブによる、患者住所地が北塩原村である在院者数と入院先。別表第二 三の項㈠⑤が求める「当該市町村の区域における基盤整備量」を実数で定めるための起点となる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>年</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>在院者数</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>人口10万人あたり</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>入院先の内訳</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="26" customHeight="1">
+      <c r="A6" s="7" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>7 (41)</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>270.2 (135.4)</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>福島県 喜多方市 4人／福島県 会津若松市 3人</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr"/>
+    </row>
+    <row r="7" ht="26" customHeight="1">
+      <c r="A7" s="10" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>10 (40)</t>
+        </is>
+      </c>
+      <c r="C7" s="10" t="inlineStr">
+        <is>
+          <t>403.6 (132.2)</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>福島県 喜多方市 8人／福島県 会津若松市 2人</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr"/>
+    </row>
+    <row r="8" ht="26" customHeight="1">
+      <c r="A8" s="7" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>8 (38.5)</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>329.6 (128.5)</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>福島県 喜多方市 7人／福島県 会津若松市 1人</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr"/>
+    </row>
+    <row r="10" ht="30" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>※（）内は全国中央値。本村は人口10万人あたりで全国中央値の2倍を超える水準にある。母数が小さく1人の増減が大きく振れるため、率ではなく実数で扱う。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="30" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>※【要確認】ReMHRADの当該タブが「全在院者」か「1年以上の長期入院者」かを、ダウンロード時の画面表示で確認すること。現行計画は令和5年度の1年以上長期入院者を5人と記載しており、本表の2023年10人が全在院者であれば整合する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="30" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>※別表第四のCは1年以上入院患者数である。本村の値を定める際は、全在院者数ではなく1年以上の人数を用いる。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A12:E12"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="A11:E11"/>
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:E31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -9315,12 +9491,12 @@
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>ReMHRADの市町村タブ（患者住所地別）、村・会津保健所の把握。現行計画に令和5年度5人の記載あり</t>
+          <t>ReMHRAD市町村タブで在院者数を取得済み（06シート。2022年7人・2023年10人・2024年8人）。ただし全在院者か1年以上かの区別、及び年齢区分の内訳は村・会津保健所への照会が必要</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>村・県照会</t>
+          <t>一部取得</t>
         </is>
       </c>
     </row>

--- a/output/福島県_精神医療指標抽出.xlsx
+++ b/output/福島県_精神医療指標抽出.xlsx
@@ -8837,7 +8837,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -8857,7 +8857,7 @@
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>ReMHRAD 市町村タブによる、患者住所地が北塩原村である在院者数と入院先。別表第二 三の項㈠⑤が求める「当該市町村の区域における基盤整備量」を実数で定めるための起点となる。</t>
+          <t>ReMHRAD「在・退院者の状況」タブの指標「在院患者数_患者の住所ベース」（出典：630調査）による。入院期間による絞り込みはなく、患者住所地が北塩原村である全在院患者数である。別表第四のCが求める1年以上入院患者数とは範囲が異なることに注意。</t>
         </is>
       </c>
     </row>
@@ -8961,24 +8961,32 @@
     <row r="11" ht="30" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>※【要確認】ReMHRADの当該タブが「全在院者」か「1年以上の長期入院者」かを、ダウンロード時の画面表示で確認すること。現行計画は令和5年度の1年以上長期入院者を5人と記載しており、本表の2023年10人が全在院者であれば整合する。</t>
+          <t>※【確定】ReMHRAD「ReMHRADについて」のデータソース一覧により、本表の指標は「在院患者数_患者の住所ベース」（出典：630調査）であり、入院期間による絞り込みはない。すなわち全在院患者数である。</t>
         </is>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>※別表第四のCは1年以上入院患者数である。本村の値を定める際は、全在院者数ではなく1年以上の人数を用いる。</t>
+          <t>※現行計画は令和5年度の1年以上長期入院者を5人と記載しており、本表の令和5年（2023年）10人が全在院患者であることと矛盾しない（10人のうち5人が1年以上）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="30" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>※別表第四のCは1年以上入院患者数である。本村の基盤整備量を定める際は、本表の全在院患者数ではなく1年以上の人数を用いること。1年以上の人数と年齢区分（65歳未満／65歳以上／75歳以上／40歳以上の認知症）の内訳は、村・会津保健所への照会が必要。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="6">
     <mergeCell ref="A12:E12"/>
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A10:E10"/>
     <mergeCell ref="A11:E11"/>
     <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A13:E13"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
